--- a/public/assets/tamplate.xlsx
+++ b/public/assets/tamplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bayu\Documents\polda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\polda-liveware\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97E04742-08EB-4E7A-A06A-8C9210FE077B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157D03CB-22F0-424C-AC9A-DD42ED4AFAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>No.</t>
   </si>
@@ -41,28 +41,22 @@
     <t>Nama Lengkap</t>
   </si>
   <si>
-    <t>Pangkat</t>
-  </si>
-  <si>
-    <t>Nrp</t>
-  </si>
-  <si>
     <t>Jabatan</t>
   </si>
   <si>
-    <t>KOMBES POL</t>
-  </si>
-  <si>
-    <t>DIRRESKRIMSUS POLDA NTB</t>
-  </si>
-  <si>
-    <t>DAFTAR NAMA PERSONEL DITRESKRIMSUS POLDA NTB</t>
-  </si>
-  <si>
     <t>Fulan</t>
   </si>
   <si>
     <t>123445</t>
+  </si>
+  <si>
+    <t>Nip</t>
+  </si>
+  <si>
+    <t>Dosen</t>
+  </si>
+  <si>
+    <t>DAFTAR DOSEN/PEGAWAI KAMPUS PNB</t>
   </si>
 </sst>
 </file>
@@ -425,26 +419,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="89.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -452,35 +444,29 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
